--- a/Seep-Logos-agents/titles/Umbrella/sns/umbrella-sns-plan-phase1.xlsx
+++ b/Seep-Logos-agents/titles/Umbrella/sns/umbrella-sns-plan-phase1.xlsx
@@ -802,7 +802,7 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Umbrella 公式アカウントです。
-いつか、この場所から何かをお届けできる日を楽しみにしています。
+いつか、この場所から何かをお伝えできる日を楽しみにしています。
 #Umbrella</t>
         </is>
       </c>
@@ -912,7 +912,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>まもなく、お届けします。
+          <t>もうすぐ、明かされます。
 フォローしてお待ちください。
 #Umbrella</t>
         </is>
